--- a/artfynd/A 8172-2026 artfynd.xlsx
+++ b/artfynd/A 8172-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127736253</v>
+        <v>127736252</v>
       </c>
       <c r="B2" t="n">
-        <v>96444</v>
+        <v>96979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,19 +705,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504924</v>
+        <v>504915</v>
       </c>
       <c r="R2" t="n">
-        <v>6614059</v>
+        <v>6614037</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,12 +772,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Traktorväg</t>
+          <t>Jordtipp</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Kring gammal häst eller älgspillning</t>
+          <t>Basen på jordhögarna</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,14 +795,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127736252</v>
+        <v>127736253</v>
       </c>
       <c r="B3" t="n">
-        <v>96444</v>
+        <v>96979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,15 +825,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504915</v>
+        <v>504924</v>
       </c>
       <c r="R3" t="n">
-        <v>6614037</v>
+        <v>6614059</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,12 +896,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Jordtipp</t>
+          <t>Traktorväg</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Basen på jordhögarna</t>
+          <t>Kring gammal häst eller älgspillning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,6 +916,786 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104518063</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87375</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>505020</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6614019</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104518062</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>505031</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6614048</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104518064</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505024</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6614016</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104518169</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505024</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6613998</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104518066</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504982</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6613944</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104518147</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>505014</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6614037</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104518053</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fanthyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>505015</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6614057</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129289754</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Larsboda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504865</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6613935</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henric Ernstson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henric Ernstson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8172-2026 artfynd.xlsx
+++ b/artfynd/A 8172-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736253</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518063</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518062</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518064</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518169</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518066</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518147</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518053</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,8 +1746,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>